--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="C3" t="n">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="C10" t="n">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="F12" t="n">
-        <v>170</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
-        <v>150</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>27</v>
-      </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="F15" t="n">
-        <v>131</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="F16" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="F18" t="n">
-        <v>174</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C20" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="n">
         <v>16</v>
-      </c>
-      <c r="E20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F20" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="F21" t="n">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F24" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
@@ -964,13 +964,13 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C29" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F29" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C35" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="F35" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -458,7 +458,7 @@
         <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -467,7 +467,7 @@
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -486,10 +486,10 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
         <v>11</v>
@@ -612,16 +612,16 @@
         <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
         <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -637,13 +637,13 @@
         <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -684,10 +684,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>145</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -722,7 +722,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -810,16 +810,16 @@
         <v>147</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -882,10 +882,10 @@
         <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
         <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -1058,10 +1058,10 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1190,10 +1190,10 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="F3" t="n">
-        <v>169</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D9" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" t="n">
         <v>62</v>
       </c>
-      <c r="E9" t="n">
-        <v>69</v>
-      </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>103</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>153</v>
+      </c>
+      <c r="F13" t="n">
         <v>8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="n">
-        <v>131</v>
-      </c>
-      <c r="F13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>175</v>
+      </c>
+      <c r="F18" t="n">
         <v>8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E18" t="n">
-        <v>164</v>
-      </c>
-      <c r="F18" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -920,13 +920,13 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
         <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -986,13 +986,13 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1008,16 +1008,16 @@
         <v>43</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1118,13 +1118,13 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>47</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1206,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -555,7 +555,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -612,16 +612,16 @@
         <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
         <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>233</v>
       </c>
       <c r="C10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -659,10 +659,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -766,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>144</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -879,10 +879,10 @@
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F21" t="n">
         <v>19</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
         <v>29</v>
@@ -1033,10 +1033,10 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F34" t="n">
         <v>7</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>198</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -499,13 +499,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>198</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
         <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>216</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
         <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>22</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E24" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>4</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>11</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
         <v>2</v>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C35" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>173</v>
       </c>
       <c r="C3" t="n">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>265</v>
+        <v>190</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
         <v>6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="C10" t="n">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C18" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="C20" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="C21" t="n">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="C24" t="n">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
         <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C27" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C29" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
         <v>9</v>
       </c>
-      <c r="C31" t="n">
-        <v>14</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
         <v>4</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>56</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48</v>
+      </c>
+      <c r="F34" t="n">
         <v>12</v>
-      </c>
-      <c r="C34" t="n">
-        <v>46</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" t="n">
-        <v>56</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E35" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
         <v>15</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>16</v>
-      </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
         <v>91</v>
@@ -590,10 +590,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -612,16 +612,16 @@
         <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -634,7 +634,7 @@
         <v>206</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
         <v>32</v>
@@ -643,7 +643,7 @@
         <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -662,10 +662,10 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
         <v>13</v>
-      </c>
-      <c r="D12" t="n">
-        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>187</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -706,10 +706,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -722,10 +722,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>185</v>
@@ -860,10 +860,10 @@
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" t="n">
         <v>16</v>
@@ -882,10 +882,10 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -920,10 +920,10 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
@@ -951,7 +951,7 @@
         <v>117</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="n">
         <v>18</v>
@@ -1061,7 +1061,7 @@
         <v>78</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1140,13 +1140,13 @@
         <v>42</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>91</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -524,10 +524,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -546,16 +546,16 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -590,16 +590,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
         <v>32</v>
       </c>
-      <c r="E10" t="n">
-        <v>190</v>
-      </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>30</v>
-      </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -750,10 +750,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
@@ -772,10 +772,10 @@
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -794,10 +794,10 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>110</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>194</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1036,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1162,16 +1162,16 @@
         <v>56</v>
       </c>
       <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
         <v>5</v>
       </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="n">
-        <v>48</v>
-      </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="n">
         <v>14</v>
       </c>
-      <c r="D35" t="n">
-        <v>12</v>
-      </c>
-      <c r="E35" t="n">
-        <v>103</v>
-      </c>
       <c r="F35" t="n">
-        <v>22</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
@@ -1212,10 +1212,10 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>138</v>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C10" t="n">
         <v>25</v>
@@ -643,7 +643,7 @@
         <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17">
@@ -810,7 +810,7 @@
         <v>145</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -819,7 +819,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22">
@@ -945,10 +945,10 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
         <v>130</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>4</v>
